--- a/Documents/Sub-lang-country-F2H26-Translation Document - SESAR.xlsx
+++ b/Documents/Sub-lang-country-F2H26-Translation Document - SESAR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rami.o\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\Y7KLZ8SI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Adobe-Form-Builder-main\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897419D7-17B3-4A90-9EE8-F802216BA455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08C119D-DE1A-45AE-A724-6080DF29AF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5370" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1710" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Complete Translations" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="173">
   <si>
     <t>Translation</t>
   </si>
@@ -553,6 +553,12 @@
   </si>
   <si>
     <t>https://www.samsung.com/sa_ar/offer/ (Please update the redirection link)</t>
+  </si>
+  <si>
+    <t>Project Code</t>
+  </si>
+  <si>
+    <t>F2H26</t>
   </si>
 </sst>
 </file>
@@ -728,14 +734,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1182,16 +1188,20 @@
     </row>
     <row r="2" spans="1:4" ht="15" thickBot="1">
       <c r="A2" s="16"/>
-      <c r="B2"/>
-      <c r="C2" s="17"/>
+      <c r="B2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>172</v>
+      </c>
       <c r="D2" s="17"/>
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1">
       <c r="A3" s="8"/>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="31"/>
+      <c r="C3" s="32"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="8"/>
@@ -1345,7 +1355,7 @@
       <c r="B18" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="30" t="s">
         <v>150</v>
       </c>
       <c r="D18" s="13"/>
@@ -1357,7 +1367,7 @@
       <c r="B19" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C19" s="30" t="s">
         <v>151</v>
       </c>
       <c r="D19" s="13"/>
@@ -1369,7 +1379,7 @@
       <c r="B20" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="30" t="s">
         <v>152</v>
       </c>
       <c r="D20" s="13"/>

--- a/Documents/Sub-lang-country-F2H26-Translation Document - SESAR.xlsx
+++ b/Documents/Sub-lang-country-F2H26-Translation Document - SESAR.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Adobe-Form-Builder-main\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08C119D-DE1A-45AE-A724-6080DF29AF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC27046-D0CF-4729-815F-DA443A43B21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1710" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1812" yWindow="3816" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Complete Translations" sheetId="1" r:id="rId1"/>
     <sheet name="Samples" sheetId="5" r:id="rId2"/>
     <sheet name="Lists" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="172">
   <si>
     <t>Translation</t>
   </si>
@@ -556,9 +556,6 @@
   </si>
   <si>
     <t>Project Code</t>
-  </si>
-  <si>
-    <t>F2H26</t>
   </si>
 </sst>
 </file>
@@ -1191,9 +1188,7 @@
       <c r="B2" t="s">
         <v>171</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>172</v>
-      </c>
+      <c r="C2" s="17"/>
       <c r="D2" s="17"/>
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1">
